--- a/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/4_fold/128.xlsx
+++ b/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/4_fold/128.xlsx
@@ -426,13 +426,13 @@
         <v>-18.94636415932112</v>
       </c>
       <c r="E2">
-        <v>-13.31170048832504</v>
+        <v>-32.19532388846024</v>
       </c>
       <c r="F2">
-        <v>-1.422743527475534</v>
+        <v>-6.130242819618344</v>
       </c>
       <c r="G2">
-        <v>-11.1817227551417</v>
+        <v>-22.34721933564425</v>
       </c>
     </row>
     <row r="3" spans="1:7">
@@ -449,13 +449,13 @@
         <v>-18.80682644605714</v>
       </c>
       <c r="E3">
-        <v>-13.89087420001005</v>
+        <v>-32.28352950518164</v>
       </c>
       <c r="F3">
-        <v>-1.631003376213358</v>
+        <v>-5.905993823271684</v>
       </c>
       <c r="G3">
-        <v>-11.0131040604234</v>
+        <v>-21.28927639617263</v>
       </c>
     </row>
     <row r="4" spans="1:7">
@@ -472,13 +472,13 @@
         <v>-18.64126556104208</v>
       </c>
       <c r="E4">
-        <v>-14.37891237229069</v>
+        <v>-32.29647188389556</v>
       </c>
       <c r="F4">
-        <v>-1.328702289705318</v>
+        <v>-6.030277926550708</v>
       </c>
       <c r="G4">
-        <v>-11.0292772014899</v>
+        <v>-21.88364179128279</v>
       </c>
     </row>
     <row r="5" spans="1:7">
@@ -495,13 +495,13 @@
         <v>-18.46467271042467</v>
       </c>
       <c r="E5">
-        <v>-14.52707045639964</v>
+        <v>-32.75586519384068</v>
       </c>
       <c r="F5">
-        <v>-1.288554635161237</v>
+        <v>-6.376706144605878</v>
       </c>
       <c r="G5">
-        <v>-9.937394946818161</v>
+        <v>-21.23433070054895</v>
       </c>
     </row>
     <row r="6" spans="1:7">
@@ -518,13 +518,13 @@
         <v>-18.2704426839043</v>
       </c>
       <c r="E6">
-        <v>-16.71825411754308</v>
+        <v>-33.84796330671549</v>
       </c>
       <c r="F6">
-        <v>-1.317161475049515</v>
+        <v>-6.040757602563525</v>
       </c>
       <c r="G6">
-        <v>-9.638423163207797</v>
+        <v>-21.15161438625691</v>
       </c>
     </row>
     <row r="7" spans="1:7">
@@ -541,13 +541,13 @@
         <v>-18.06151566371555</v>
       </c>
       <c r="E7">
-        <v>-17.22710968483698</v>
+        <v>-35.97291803549675</v>
       </c>
       <c r="F7">
-        <v>-1.018608751039142</v>
+        <v>-5.977260756036734</v>
       </c>
       <c r="G7">
-        <v>-9.816878960161317</v>
+        <v>-20.85288377243116</v>
       </c>
     </row>
     <row r="8" spans="1:7">
@@ -564,13 +564,13 @@
         <v>-17.83462434330126</v>
       </c>
       <c r="E8">
-        <v>-17.21342916485981</v>
+        <v>-34.93992556537006</v>
       </c>
       <c r="F8">
-        <v>-1.398349764197894</v>
+        <v>-6.024583729023864</v>
       </c>
       <c r="G8">
-        <v>-9.649247913132404</v>
+        <v>-21.42862003213757</v>
       </c>
     </row>
     <row r="9" spans="1:7">
@@ -587,13 +587,13 @@
         <v>-17.59148202822841</v>
       </c>
       <c r="E9">
-        <v>-17.679354798561</v>
+        <v>-34.61805521832687</v>
       </c>
       <c r="F9">
-        <v>-1.247586896888384</v>
+        <v>-5.845126214881379</v>
       </c>
       <c r="G9">
-        <v>-8.454879984272969</v>
+        <v>-21.01174739545324</v>
       </c>
     </row>
     <row r="10" spans="1:7">
@@ -610,13 +610,13 @@
         <v>-17.33436121192996</v>
       </c>
       <c r="E10">
-        <v>-19.16682265586048</v>
+        <v>-35.50594179582578</v>
       </c>
       <c r="F10">
-        <v>-0.7162621043239479</v>
+        <v>-5.888985783757405</v>
       </c>
       <c r="G10">
-        <v>-7.938986643367714</v>
+        <v>-20.38874349857225</v>
       </c>
     </row>
     <row r="11" spans="1:7">
@@ -633,13 +633,13 @@
         <v>-17.05726686964708</v>
       </c>
       <c r="E11">
-        <v>-19.399740187971</v>
+        <v>-36.04228746458325</v>
       </c>
       <c r="F11">
-        <v>-0.4921638708445976</v>
+        <v>-5.745211852225314</v>
       </c>
       <c r="G11">
-        <v>-8.061920890313869</v>
+        <v>-20.52688456683565</v>
       </c>
     </row>
     <row r="12" spans="1:7">
@@ -656,13 +656,13 @@
         <v>-16.76399403276245</v>
       </c>
       <c r="E12">
-        <v>-19.87604961257178</v>
+        <v>-36.88772186249725</v>
       </c>
       <c r="F12">
-        <v>-0.822006516760916</v>
+        <v>-5.910622740318527</v>
       </c>
       <c r="G12">
-        <v>-7.048584517332117</v>
+        <v>-20.8565948340149</v>
       </c>
     </row>
     <row r="13" spans="1:7">
@@ -679,13 +679,13 @@
         <v>-16.44910433858269</v>
       </c>
       <c r="E13">
-        <v>-20.97684918825232</v>
+        <v>-36.95477950560284</v>
       </c>
       <c r="F13">
-        <v>-0.6416262013317124</v>
+        <v>-5.803505723095121</v>
       </c>
       <c r="G13">
-        <v>-6.255762639252847</v>
+        <v>-20.07909462000745</v>
       </c>
     </row>
     <row r="14" spans="1:7">
@@ -702,13 +702,13 @@
         <v>-16.13000590844434</v>
       </c>
       <c r="E14">
-        <v>-21.81127033737966</v>
+        <v>-37.21042544875785</v>
       </c>
       <c r="F14">
-        <v>-0.4529042261563179</v>
+        <v>-5.725407244359183</v>
       </c>
       <c r="G14">
-        <v>-6.744763088256893</v>
+        <v>-18.63882046320777</v>
       </c>
     </row>
     <row r="15" spans="1:7">
@@ -725,13 +725,13 @@
         <v>-15.80131668921851</v>
       </c>
       <c r="E15">
-        <v>-22.14951564643459</v>
+        <v>-38.19014947913231</v>
       </c>
       <c r="F15">
-        <v>-0.4038367114188919</v>
+        <v>-5.15456932668121</v>
       </c>
       <c r="G15">
-        <v>-6.219413266817319</v>
+        <v>-19.57512687886</v>
       </c>
     </row>
     <row r="16" spans="1:7">
@@ -748,13 +748,13 @@
         <v>-15.47089488691309</v>
       </c>
       <c r="E16">
-        <v>-23.74564876602212</v>
+        <v>-39.13744737137485</v>
       </c>
       <c r="F16">
-        <v>-0.2698631946293223</v>
+        <v>-5.445267470978238</v>
       </c>
       <c r="G16">
-        <v>-5.459945005889804</v>
+        <v>-18.61560253945314</v>
       </c>
     </row>
     <row r="17" spans="1:7">
@@ -771,13 +771,13 @@
         <v>-15.13526876628155</v>
       </c>
       <c r="E17">
-        <v>-23.55045795086951</v>
+        <v>-39.10750283699913</v>
       </c>
       <c r="F17">
-        <v>0.2371009693535863</v>
+        <v>-5.219282216555311</v>
       </c>
       <c r="G17">
-        <v>-4.75259566821251</v>
+        <v>-18.95546818735886</v>
       </c>
     </row>
     <row r="18" spans="1:7">
@@ -794,13 +794,13 @@
         <v>-14.80134067370317</v>
       </c>
       <c r="E18">
-        <v>-25.45507977680757</v>
+        <v>-40.13056209938999</v>
       </c>
       <c r="F18">
-        <v>0.1129270389391348</v>
+        <v>-5.18984618089683</v>
       </c>
       <c r="G18">
-        <v>-4.4347437357491</v>
+        <v>-18.70619378548785</v>
       </c>
     </row>
     <row r="19" spans="1:7">
@@ -817,13 +817,13 @@
         <v>-14.46693147952738</v>
       </c>
       <c r="E19">
-        <v>-26.18190891198668</v>
+        <v>-39.41264726529499</v>
       </c>
       <c r="F19">
-        <v>0.3278627005761198</v>
+        <v>-5.182756184296269</v>
       </c>
       <c r="G19">
-        <v>-4.179474542088979</v>
+        <v>-18.22459741293269</v>
       </c>
     </row>
     <row r="20" spans="1:7">
@@ -840,13 +840,13 @@
         <v>-14.12879916103946</v>
       </c>
       <c r="E20">
-        <v>-25.79493722260922</v>
+        <v>-40.82697800313359</v>
       </c>
       <c r="F20">
-        <v>0.710123607374188</v>
+        <v>-4.947581021906684</v>
       </c>
       <c r="G20">
-        <v>-3.17510574762919</v>
+        <v>-17.93134972033278</v>
       </c>
     </row>
     <row r="21" spans="1:7">
@@ -863,13 +863,13 @@
         <v>-13.78579150603539</v>
       </c>
       <c r="E21">
-        <v>-26.65481745260769</v>
+        <v>-40.90537720939138</v>
       </c>
       <c r="F21">
-        <v>0.3956156988184941</v>
+        <v>-4.730582725436729</v>
       </c>
       <c r="G21">
-        <v>-2.888976665202492</v>
+        <v>-17.47682342564304</v>
       </c>
     </row>
     <row r="22" spans="1:7">
@@ -886,13 +886,13 @@
         <v>-13.437926530403</v>
       </c>
       <c r="E22">
-        <v>-27.75292258625367</v>
+        <v>-41.3299918389576</v>
       </c>
       <c r="F22">
-        <v>1.069490924261086</v>
+        <v>-5.112373947917409</v>
       </c>
       <c r="G22">
-        <v>-3.364734103992619</v>
+        <v>-17.19361298979346</v>
       </c>
     </row>
     <row r="23" spans="1:7">
@@ -909,13 +909,13 @@
         <v>-13.09731715377613</v>
       </c>
       <c r="E23">
-        <v>-28.50041061985577</v>
+        <v>-42.65525202153933</v>
       </c>
       <c r="F23">
-        <v>1.132581042393102</v>
+        <v>-4.491710559328449</v>
       </c>
       <c r="G23">
-        <v>-3.427454654101405</v>
+        <v>-17.639434203686</v>
       </c>
     </row>
     <row r="24" spans="1:7">
@@ -932,13 +932,13 @@
         <v>-12.76489482249851</v>
       </c>
       <c r="E24">
-        <v>-29.09015378987468</v>
+        <v>-41.68584838342835</v>
       </c>
       <c r="F24">
-        <v>0.8331626744468043</v>
+        <v>-4.830289167874691</v>
       </c>
       <c r="G24">
-        <v>-2.776086237449796</v>
+        <v>-17.26456940601646</v>
       </c>
     </row>
     <row r="25" spans="1:7">
@@ -955,13 +955,13 @@
         <v>-12.45144830106102</v>
       </c>
       <c r="E25">
-        <v>-28.96597397563635</v>
+        <v>-42.26041890128456</v>
       </c>
       <c r="F25">
-        <v>1.2724806995823</v>
+        <v>-4.618496332163927</v>
       </c>
       <c r="G25">
-        <v>-3.252732887282533</v>
+        <v>-17.16550932713682</v>
       </c>
     </row>
     <row r="26" spans="1:7">
@@ -978,13 +978,13 @@
         <v>-12.1585131267209</v>
       </c>
       <c r="E26">
-        <v>-28.62761998320524</v>
+        <v>-43.41485825158595</v>
       </c>
       <c r="F26">
-        <v>0.9587398592415981</v>
+        <v>-4.598147486914158</v>
       </c>
       <c r="G26">
-        <v>-2.923721520295452</v>
+        <v>-16.99659040064583</v>
       </c>
     </row>
     <row r="27" spans="1:7">
@@ -1001,13 +1001,13 @@
         <v>-11.90120251966781</v>
       </c>
       <c r="E27">
-        <v>-28.10887422867858</v>
+        <v>-41.64915415854419</v>
       </c>
       <c r="F27">
-        <v>1.341448912804581</v>
+        <v>-4.507627638973242</v>
       </c>
       <c r="G27">
-        <v>-2.907633690989494</v>
+        <v>-17.11114276711838</v>
       </c>
     </row>
     <row r="28" spans="1:7">
@@ -1024,13 +1024,13 @@
         <v>-11.67807209153883</v>
       </c>
       <c r="E28">
-        <v>-29.09350486064036</v>
+        <v>-42.75189871381103</v>
       </c>
       <c r="F28">
-        <v>1.001780172756255</v>
+        <v>-4.502318632288699</v>
       </c>
       <c r="G28">
-        <v>-2.981021492388034</v>
+        <v>-17.34194061038816</v>
       </c>
     </row>
     <row r="29" spans="1:7">
@@ -1047,13 +1047,13 @@
         <v>-11.49337746065192</v>
       </c>
       <c r="E29">
-        <v>-29.48854629069948</v>
+        <v>-42.50469158196931</v>
       </c>
       <c r="F29">
-        <v>1.357201147336216</v>
+        <v>-4.64904569361177</v>
       </c>
       <c r="G29">
-        <v>-3.312172215831874</v>
+        <v>-17.96206195412918</v>
       </c>
     </row>
     <row r="30" spans="1:7">
@@ -1070,13 +1070,13 @@
         <v>-11.34535751813203</v>
       </c>
       <c r="E30">
-        <v>-29.02814086681364</v>
+        <v>-42.0390489778936</v>
       </c>
       <c r="F30">
-        <v>0.9465413208679725</v>
+        <v>-4.486388298765462</v>
       </c>
       <c r="G30">
-        <v>-3.514613742384934</v>
+        <v>-17.68682324605828</v>
       </c>
     </row>
     <row r="31" spans="1:7">
@@ -1093,13 +1093,13 @@
         <v>-11.23596367352896</v>
       </c>
       <c r="E31">
-        <v>-28.21692814697561</v>
+        <v>-42.45290168898059</v>
       </c>
       <c r="F31">
-        <v>1.006828243708915</v>
+        <v>-4.306681446034735</v>
       </c>
       <c r="G31">
-        <v>-3.591499325965843</v>
+        <v>-18.10639304686447</v>
       </c>
     </row>
     <row r="32" spans="1:7">
@@ -1116,13 +1116,13 @@
         <v>-11.16421230692132</v>
       </c>
       <c r="E32">
-        <v>-27.47077148473176</v>
+        <v>-41.77765640122286</v>
       </c>
       <c r="F32">
-        <v>1.108667732209086</v>
+        <v>-4.454159008224742</v>
       </c>
       <c r="G32">
-        <v>-3.486703671800297</v>
+        <v>-17.25758040409484</v>
       </c>
     </row>
     <row r="33" spans="1:7">
@@ -1139,13 +1139,13 @@
         <v>-11.12272169820446</v>
       </c>
       <c r="E33">
-        <v>-27.75851978012715</v>
+        <v>-42.52417760562432</v>
       </c>
       <c r="F33">
-        <v>0.8505484494967602</v>
+        <v>-4.488115444800299</v>
       </c>
       <c r="G33">
-        <v>-4.278547745854853</v>
+        <v>-17.69739042009047</v>
       </c>
     </row>
     <row r="34" spans="1:7">
@@ -1162,13 +1162,13 @@
         <v>-11.10977757079958</v>
       </c>
       <c r="E34">
-        <v>-27.14694030844326</v>
+        <v>-41.58535022401313</v>
       </c>
       <c r="F34">
-        <v>0.9402357881978627</v>
+        <v>-4.843189333438487</v>
       </c>
       <c r="G34">
-        <v>-4.359311733319025</v>
+        <v>-18.22833636489968</v>
       </c>
     </row>
     <row r="35" spans="1:7">
@@ -1185,13 +1185,13 @@
         <v>-11.11704891223695</v>
       </c>
       <c r="E35">
-        <v>-25.95408591313479</v>
+        <v>-41.29344478947869</v>
       </c>
       <c r="F35">
-        <v>0.9328467509648911</v>
+        <v>-4.918566625256228</v>
       </c>
       <c r="G35">
-        <v>-4.651878572445354</v>
+        <v>-17.87611035537952</v>
       </c>
     </row>
     <row r="36" spans="1:7">
@@ -1208,13 +1208,13 @@
         <v>-11.14856660303726</v>
       </c>
       <c r="E36">
-        <v>-25.30682206627045</v>
+        <v>-40.45692242841179</v>
       </c>
       <c r="F36">
-        <v>0.9093360273386355</v>
+        <v>-4.729771753749388</v>
       </c>
       <c r="G36">
-        <v>-4.741344359485174</v>
+        <v>-17.98728470425663</v>
       </c>
     </row>
     <row r="37" spans="1:7">
@@ -1231,13 +1231,13 @@
         <v>-11.19145568618299</v>
       </c>
       <c r="E37">
-        <v>-25.539169010656</v>
+        <v>-40.92295674548916</v>
       </c>
       <c r="F37">
-        <v>1.264844808863294</v>
+        <v>-4.522983085518936</v>
       </c>
       <c r="G37">
-        <v>-4.678111938813115</v>
+        <v>-18.26405902401735</v>
       </c>
     </row>
     <row r="38" spans="1:7">
@@ -1254,13 +1254,13 @@
         <v>-11.24512624527863</v>
       </c>
       <c r="E38">
-        <v>-25.09622085406973</v>
+        <v>-40.82553115568814</v>
       </c>
       <c r="F38">
-        <v>1.403778589660827</v>
+        <v>-4.726947849273245</v>
       </c>
       <c r="G38">
-        <v>-5.103814342713912</v>
+        <v>-18.02605889942459</v>
       </c>
     </row>
     <row r="39" spans="1:7">
@@ -1277,13 +1277,13 @@
         <v>-11.30307548106873</v>
       </c>
       <c r="E39">
-        <v>-24.02522316583367</v>
+        <v>-39.21928142516746</v>
       </c>
       <c r="F39">
-        <v>0.8856215253312912</v>
+        <v>-4.826727188042653</v>
       </c>
       <c r="G39">
-        <v>-5.334395625360771</v>
+        <v>-18.36524533446751</v>
       </c>
     </row>
     <row r="40" spans="1:7">
@@ -1300,13 +1300,13 @@
         <v>-11.36903771422311</v>
       </c>
       <c r="E40">
-        <v>-23.51859560775154</v>
+        <v>-39.56676255696102</v>
       </c>
       <c r="F40">
-        <v>1.281216662212223</v>
+        <v>-4.601374806315464</v>
       </c>
       <c r="G40">
-        <v>-5.302626838222227</v>
+        <v>-18.21519671316488</v>
       </c>
     </row>
     <row r="41" spans="1:7">
@@ -1323,13 +1323,13 @@
         <v>-11.43989712884808</v>
       </c>
       <c r="E41">
-        <v>-23.24431046558096</v>
+        <v>-38.62501657385189</v>
       </c>
       <c r="F41">
-        <v>1.347479427496961</v>
+        <v>-4.288201397645681</v>
       </c>
       <c r="G41">
-        <v>-5.135750472151988</v>
+        <v>-18.64033474695745</v>
       </c>
     </row>
     <row r="42" spans="1:7">
@@ -1346,13 +1346,13 @@
         <v>-11.51743903557464</v>
       </c>
       <c r="E42">
-        <v>-21.86456594797594</v>
+        <v>-39.35340350408964</v>
       </c>
       <c r="F42">
-        <v>0.9572968432259213</v>
+        <v>-4.612232217863958</v>
       </c>
       <c r="G42">
-        <v>-5.640172662485424</v>
+        <v>-18.61053633336536</v>
       </c>
     </row>
     <row r="43" spans="1:7">
@@ -1369,13 +1369,13 @@
         <v>-11.60565405021471</v>
       </c>
       <c r="E43">
-        <v>-21.24927312760575</v>
+        <v>-39.09146751053797</v>
       </c>
       <c r="F43">
-        <v>0.9398166342920461</v>
+        <v>-4.488329991957624</v>
       </c>
       <c r="G43">
-        <v>-6.130784191275158</v>
+        <v>-18.82226371693165</v>
       </c>
     </row>
     <row r="44" spans="1:7">
@@ -1392,13 +1392,13 @@
         <v>-11.7080251888734</v>
       </c>
       <c r="E44">
-        <v>-22.52590429205611</v>
+        <v>-38.26462702689946</v>
       </c>
       <c r="F44">
-        <v>1.392620480745117</v>
+        <v>-4.51711658757231</v>
       </c>
       <c r="G44">
-        <v>-6.048412405246857</v>
+        <v>-18.83529016652264</v>
       </c>
     </row>
     <row r="45" spans="1:7">
@@ -1415,13 +1415,13 @@
         <v>-11.83092966529964</v>
       </c>
       <c r="E45">
-        <v>-20.79359543058392</v>
+        <v>-37.32608720338776</v>
       </c>
       <c r="F45">
-        <v>1.526701685297051</v>
+        <v>-4.587830999279692</v>
       </c>
       <c r="G45">
-        <v>-6.472766227086724</v>
+        <v>-18.32449584392077</v>
       </c>
     </row>
     <row r="46" spans="1:7">
@@ -1438,13 +1438,13 @@
         <v>-11.96983815175282</v>
       </c>
       <c r="E46">
-        <v>-19.41880053506928</v>
+        <v>-37.4351577640995</v>
       </c>
       <c r="F46">
-        <v>1.156288917461224</v>
+        <v>-4.34587150786118</v>
       </c>
       <c r="G46">
-        <v>-5.968399817519797</v>
+        <v>-18.66943754157895</v>
       </c>
     </row>
     <row r="47" spans="1:7">
@@ -1461,13 +1461,13 @@
         <v>-12.12995125596161</v>
       </c>
       <c r="E47">
-        <v>-19.3957279600002</v>
+        <v>-37.64648353214145</v>
       </c>
       <c r="F47">
-        <v>1.231401960077472</v>
+        <v>-4.627107211316028</v>
       </c>
       <c r="G47">
-        <v>-6.690570432981104</v>
+        <v>-18.58980885677434</v>
       </c>
     </row>
     <row r="48" spans="1:7">
@@ -1484,13 +1484,13 @@
         <v>-12.30726709568347</v>
       </c>
       <c r="E48">
-        <v>-18.87115858789969</v>
+        <v>-37.17466861799328</v>
       </c>
       <c r="F48">
-        <v>1.528991292798389</v>
+        <v>-4.353539704908894</v>
       </c>
       <c r="G48">
-        <v>-6.619502455225091</v>
+        <v>-19.01501251499811</v>
       </c>
     </row>
     <row r="49" spans="1:7">
@@ -1507,13 +1507,13 @@
         <v>-12.50733379763627</v>
       </c>
       <c r="E49">
-        <v>-19.1399099348329</v>
+        <v>-36.6288040968717</v>
       </c>
       <c r="F49">
-        <v>1.561680327247663</v>
+        <v>-4.378708820075555</v>
       </c>
       <c r="G49">
-        <v>-6.645207544921781</v>
+        <v>-18.77236289945561</v>
       </c>
     </row>
     <row r="50" spans="1:7">
@@ -1530,13 +1530,13 @@
         <v>-12.71805713420985</v>
       </c>
       <c r="E50">
-        <v>-17.13142755752892</v>
+        <v>-36.06137045405157</v>
       </c>
       <c r="F50">
-        <v>1.410630844816784</v>
+        <v>-4.207863841819976</v>
       </c>
       <c r="G50">
-        <v>-7.116889706535078</v>
+        <v>-19.34268678419971</v>
       </c>
     </row>
     <row r="51" spans="1:7">
@@ -1553,13 +1553,13 @@
         <v>-12.93856593415784</v>
       </c>
       <c r="E51">
-        <v>-16.59058737831884</v>
+        <v>-34.84399663622857</v>
       </c>
       <c r="F51">
-        <v>1.238800937719277</v>
+        <v>-4.35899781772594</v>
       </c>
       <c r="G51">
-        <v>-6.940379673966309</v>
+        <v>-18.92723327583984</v>
       </c>
     </row>
     <row r="52" spans="1:7">
@@ -1576,13 +1576,13 @@
         <v>-13.16124061115415</v>
       </c>
       <c r="E52">
-        <v>-16.59350371557978</v>
+        <v>-35.52504742766414</v>
       </c>
       <c r="F52">
-        <v>1.344033419101315</v>
+        <v>-4.191331285194903</v>
       </c>
       <c r="G52">
-        <v>-7.085127481839653</v>
+        <v>-19.26329926917973</v>
       </c>
     </row>
     <row r="53" spans="1:7">
@@ -1599,13 +1599,13 @@
         <v>-13.38244945732934</v>
       </c>
       <c r="E53">
-        <v>-15.66042976019533</v>
+        <v>-35.51144615598211</v>
       </c>
       <c r="F53">
-        <v>1.305497767523082</v>
+        <v>-4.396826043542182</v>
       </c>
       <c r="G53">
-        <v>-7.298652974820517</v>
+        <v>-19.25192819586547</v>
       </c>
     </row>
     <row r="54" spans="1:7">
@@ -1622,13 +1622,13 @@
         <v>-13.59479107073969</v>
       </c>
       <c r="E54">
-        <v>-15.20791293803086</v>
+        <v>-34.14302961610728</v>
       </c>
       <c r="F54">
-        <v>1.189279477645117</v>
+        <v>-4.52183331156385</v>
       </c>
       <c r="G54">
-        <v>-7.478588602697347</v>
+        <v>-19.72163342148921</v>
       </c>
     </row>
     <row r="55" spans="1:7">
@@ -1645,13 +1645,13 @@
         <v>-13.7889661795981</v>
       </c>
       <c r="E55">
-        <v>-15.16315802941305</v>
+        <v>-35.23529981099437</v>
       </c>
       <c r="F55">
-        <v>0.9019403631664415</v>
+        <v>-4.530744888083167</v>
       </c>
       <c r="G55">
-        <v>-8.070517690799614</v>
+        <v>-19.30755146374118</v>
       </c>
     </row>
     <row r="56" spans="1:7">
@@ -1668,13 +1668,13 @@
         <v>-13.96277330552669</v>
       </c>
       <c r="E56">
-        <v>-14.3319249259871</v>
+        <v>-34.27281568116711</v>
       </c>
       <c r="F56">
-        <v>1.265603593404258</v>
+        <v>-4.618797857898547</v>
       </c>
       <c r="G56">
-        <v>-7.379663053901648</v>
+        <v>-18.61732682138263</v>
       </c>
     </row>
     <row r="57" spans="1:7">
@@ -1691,13 +1691,13 @@
         <v>-14.10939543938609</v>
       </c>
       <c r="E57">
-        <v>-13.35865170683657</v>
+        <v>-33.83258234474844</v>
       </c>
       <c r="F57">
-        <v>1.10556798138781</v>
+        <v>-4.476548122387607</v>
       </c>
       <c r="G57">
-        <v>-8.544070148701795</v>
+        <v>-19.10723616875864</v>
       </c>
     </row>
     <row r="58" spans="1:7">
@@ -1714,13 +1714,13 @@
         <v>-14.23303780067065</v>
       </c>
       <c r="E58">
-        <v>-13.70537884770785</v>
+        <v>-33.28170706713736</v>
       </c>
       <c r="F58">
-        <v>1.005902128952585</v>
+        <v>-4.319867398352497</v>
       </c>
       <c r="G58">
-        <v>-8.220732013790993</v>
+        <v>-19.97612332502896</v>
       </c>
     </row>
     <row r="59" spans="1:7">
@@ -1737,13 +1737,13 @@
         <v>-14.32317149152936</v>
       </c>
       <c r="E59">
-        <v>-13.3456232871165</v>
+        <v>-33.42842283227487</v>
       </c>
       <c r="F59">
-        <v>0.8366252501905062</v>
+        <v>-4.304089484431375</v>
       </c>
       <c r="G59">
-        <v>-8.94798524144788</v>
+        <v>-20.0318811229886</v>
       </c>
     </row>
     <row r="60" spans="1:7">
@@ -1760,13 +1760,13 @@
         <v>-14.38451411985621</v>
       </c>
       <c r="E60">
-        <v>-12.67539102008525</v>
+        <v>-33.20780010709517</v>
       </c>
       <c r="F60">
-        <v>1.091745842904698</v>
+        <v>-4.678171091494201</v>
       </c>
       <c r="G60">
-        <v>-9.192531403051735</v>
+        <v>-18.76700302403826</v>
       </c>
     </row>
     <row r="61" spans="1:7">
@@ -1783,13 +1783,13 @@
         <v>-14.41365648835222</v>
       </c>
       <c r="E61">
-        <v>-13.1978501232982</v>
+        <v>-33.40837074936891</v>
       </c>
       <c r="F61">
-        <v>0.7566977362291875</v>
+        <v>-4.759524225755738</v>
       </c>
       <c r="G61">
-        <v>-8.989390976306513</v>
+        <v>-19.29724678743374</v>
       </c>
     </row>
     <row r="62" spans="1:7">
@@ -1806,13 +1806,13 @@
         <v>-14.41738497784106</v>
       </c>
       <c r="E62">
-        <v>-12.54625252680852</v>
+        <v>-32.81460403019418</v>
       </c>
       <c r="F62">
-        <v>1.148432681013074</v>
+        <v>-4.53286136679732</v>
       </c>
       <c r="G62">
-        <v>-9.271907433796262</v>
+        <v>-19.938190763191</v>
       </c>
     </row>
     <row r="63" spans="1:7">
@@ -1829,13 +1829,13 @@
         <v>-14.39199382596376</v>
       </c>
       <c r="E63">
-        <v>-12.5226863480726</v>
+        <v>-32.15613447439786</v>
       </c>
       <c r="F63">
-        <v>0.731740683117644</v>
+        <v>-4.510916257562355</v>
       </c>
       <c r="G63">
-        <v>-8.673724337401692</v>
+        <v>-20.51212727287205</v>
       </c>
     </row>
     <row r="64" spans="1:7">
@@ -1852,13 +1852,13 @@
         <v>-14.33835544526451</v>
       </c>
       <c r="E64">
-        <v>-11.92942908222374</v>
+        <v>-32.06556499424445</v>
       </c>
       <c r="F64">
-        <v>0.7129831316486519</v>
+        <v>-4.597545263812322</v>
       </c>
       <c r="G64">
-        <v>-9.417833200209447</v>
+        <v>-19.75222096886635</v>
       </c>
     </row>
     <row r="65" spans="1:7">
@@ -1875,13 +1875,13 @@
         <v>-14.25669143845675</v>
       </c>
       <c r="E65">
-        <v>-12.39424071131904</v>
+        <v>-32.51833541095336</v>
       </c>
       <c r="F65">
-        <v>0.7461509624567442</v>
+        <v>-4.635212786352422</v>
       </c>
       <c r="G65">
-        <v>-9.055697901579771</v>
+        <v>-19.78297913976458</v>
       </c>
     </row>
     <row r="66" spans="1:7">
@@ -1898,13 +1898,13 @@
         <v>-14.14845641274395</v>
       </c>
       <c r="E66">
-        <v>-11.95277789420729</v>
+        <v>-31.44874607813368</v>
       </c>
       <c r="F66">
-        <v>0.4734391595767021</v>
+        <v>-4.705457513742417</v>
       </c>
       <c r="G66">
-        <v>-9.338489981680514</v>
+        <v>-19.65055560006851</v>
       </c>
     </row>
     <row r="67" spans="1:7">
@@ -1921,13 +1921,13 @@
         <v>-14.01940333849774</v>
       </c>
       <c r="E67">
-        <v>-11.13796503753315</v>
+        <v>-31.82892052802562</v>
       </c>
       <c r="F67">
-        <v>0.7105361343407822</v>
+        <v>-4.718248334809044</v>
       </c>
       <c r="G67">
-        <v>-9.074811017163537</v>
+        <v>-20.04489608830414</v>
       </c>
     </row>
     <row r="68" spans="1:7">
@@ -1944,13 +1944,13 @@
         <v>-13.86622215896135</v>
       </c>
       <c r="E68">
-        <v>-12.38626154011753</v>
+        <v>-33.06208513471336</v>
       </c>
       <c r="F68">
-        <v>0.5724091833935758</v>
+        <v>-4.530348928464629</v>
       </c>
       <c r="G68">
-        <v>-9.681636851145683</v>
+        <v>-20.10343636214619</v>
       </c>
     </row>
     <row r="69" spans="1:7">
@@ -1967,13 +1967,13 @@
         <v>-13.69484483835262</v>
       </c>
       <c r="E69">
-        <v>-10.67669467511185</v>
+        <v>-31.87864317262984</v>
       </c>
       <c r="F69">
-        <v>0.7566911092899651</v>
+        <v>-4.734178668332281</v>
       </c>
       <c r="G69">
-        <v>-9.321007633211792</v>
+        <v>-19.74401955557852</v>
       </c>
     </row>
     <row r="70" spans="1:7">
@@ -1990,13 +1990,13 @@
         <v>-13.50255628655808</v>
       </c>
       <c r="E70">
-        <v>-10.69106352313819</v>
+        <v>-31.80510301898228</v>
       </c>
       <c r="F70">
-        <v>0.5174155282565223</v>
+        <v>-4.75023988390516</v>
       </c>
       <c r="G70">
-        <v>-9.018465880544753</v>
+        <v>-19.83381510538506</v>
       </c>
     </row>
     <row r="71" spans="1:7">
@@ -2013,13 +2013,13 @@
         <v>-13.30193735479361</v>
       </c>
       <c r="E71">
-        <v>-10.88788006045956</v>
+        <v>-31.99028817081495</v>
       </c>
       <c r="F71">
-        <v>0.4639129344445078</v>
+        <v>-4.861924518987604</v>
       </c>
       <c r="G71">
-        <v>-9.356448107275355</v>
+        <v>-19.75070176328433</v>
       </c>
     </row>
     <row r="72" spans="1:7">
@@ -2036,13 +2036,13 @@
         <v>-13.08887830270614</v>
       </c>
       <c r="E72">
-        <v>-11.34259319251775</v>
+        <v>-31.73339236883382</v>
       </c>
       <c r="F72">
-        <v>0.4167125598329919</v>
+        <v>-5.156588058041833</v>
       </c>
       <c r="G72">
-        <v>-9.306150261990627</v>
+        <v>-19.69773956609333</v>
       </c>
     </row>
     <row r="73" spans="1:7">
@@ -2059,13 +2059,13 @@
         <v>-12.87017028410893</v>
       </c>
       <c r="E73">
-        <v>-11.53850403503759</v>
+        <v>-32.12861720209025</v>
       </c>
       <c r="F73">
-        <v>0.1781725690532351</v>
+        <v>-4.887612192148417</v>
       </c>
       <c r="G73">
-        <v>-8.888519663126063</v>
+        <v>-19.5102636910729</v>
       </c>
     </row>
     <row r="74" spans="1:7">
@@ -2082,13 +2082,13 @@
         <v>-12.64569917296846</v>
       </c>
       <c r="E74">
-        <v>-11.35625107012489</v>
+        <v>-32.53641987190299</v>
       </c>
       <c r="F74">
-        <v>0.2937555011332529</v>
+        <v>-4.98178265523347</v>
       </c>
       <c r="G74">
-        <v>-8.725131235573514</v>
+        <v>-19.85822739378733</v>
       </c>
     </row>
     <row r="75" spans="1:7">
@@ -2105,13 +2105,13 @@
         <v>-12.42241808202331</v>
       </c>
       <c r="E75">
-        <v>-12.23792684552227</v>
+        <v>-31.61528070976576</v>
       </c>
       <c r="F75">
-        <v>0.01450705107771999</v>
+        <v>-4.973957068379224</v>
       </c>
       <c r="G75">
-        <v>-8.511540118161459</v>
+        <v>-19.04294719474444</v>
       </c>
     </row>
     <row r="76" spans="1:7">
@@ -2128,13 +2128,13 @@
         <v>-12.203577637013</v>
       </c>
       <c r="E76">
-        <v>-13.28028193565982</v>
+        <v>-32.22911988997948</v>
       </c>
       <c r="F76">
-        <v>0.3343123691743167</v>
+        <v>-5.366351393615738</v>
       </c>
       <c r="G76">
-        <v>-7.883652122989238</v>
+        <v>-18.99192419949507</v>
       </c>
     </row>
     <row r="77" spans="1:7">
@@ -2151,13 +2151,13 @@
         <v>-11.98949050641581</v>
       </c>
       <c r="E77">
-        <v>-12.72169466681368</v>
+        <v>-32.85283567200393</v>
       </c>
       <c r="F77">
-        <v>0.1595318173880378</v>
+        <v>-5.002216822325728</v>
       </c>
       <c r="G77">
-        <v>-7.801903769057232</v>
+        <v>-19.30411274354688</v>
       </c>
     </row>
     <row r="78" spans="1:7">
@@ -2174,13 +2174,13 @@
         <v>-11.78287983505462</v>
       </c>
       <c r="E78">
-        <v>-12.65710051356827</v>
+        <v>-32.01372302380464</v>
       </c>
       <c r="F78">
-        <v>0.4169942047499438</v>
+        <v>-5.338281335804473</v>
       </c>
       <c r="G78">
-        <v>-7.520876986155471</v>
+        <v>-18.78867057060605</v>
       </c>
     </row>
     <row r="79" spans="1:7">
@@ -2197,13 +2197,13 @@
         <v>-11.58172771278355</v>
       </c>
       <c r="E79">
-        <v>-13.80867333982282</v>
+        <v>-33.91490773797088</v>
       </c>
       <c r="F79">
-        <v>-0.06489527795022382</v>
+        <v>-5.226783083387661</v>
       </c>
       <c r="G79">
-        <v>-7.116787988666735</v>
+        <v>-18.60000361215954</v>
       </c>
     </row>
     <row r="80" spans="1:7">
@@ -2220,13 +2220,13 @@
         <v>-11.39391568765491</v>
       </c>
       <c r="E80">
-        <v>-14.1753529371719</v>
+        <v>-33.09764044838459</v>
       </c>
       <c r="F80">
-        <v>0.1398083895273816</v>
+        <v>-5.358955729443544</v>
       </c>
       <c r="G80">
-        <v>-7.390409054508829</v>
+        <v>-19.17892921922173</v>
       </c>
     </row>
     <row r="81" spans="1:7">
@@ -2243,13 +2243,13 @@
         <v>-11.21271367331421</v>
       </c>
       <c r="E81">
-        <v>-15.11792310255043</v>
+        <v>-33.5697836768983</v>
       </c>
       <c r="F81">
-        <v>0.3547763574930757</v>
+        <v>-5.371862521946563</v>
       </c>
       <c r="G81">
-        <v>-6.866233910387536</v>
+        <v>-18.27473611897178</v>
       </c>
     </row>
     <row r="82" spans="1:7">
@@ -2266,13 +2266,13 @@
         <v>-11.04028863904425</v>
       </c>
       <c r="E82">
-        <v>-15.50920589918319</v>
+        <v>-34.14597312421226</v>
       </c>
       <c r="F82">
-        <v>0.3905875086835011</v>
+        <v>-5.44846662588785</v>
       </c>
       <c r="G82">
-        <v>-6.317649759085534</v>
+        <v>-17.94947518822715</v>
       </c>
     </row>
     <row r="83" spans="1:7">
@@ -2289,13 +2289,13 @@
         <v>-10.8711806456582</v>
       </c>
       <c r="E83">
-        <v>-16.09068007566409</v>
+        <v>-34.47148889283162</v>
       </c>
       <c r="F83">
-        <v>0.4308494779291683</v>
+        <v>-5.405012957039196</v>
       </c>
       <c r="G83">
-        <v>-6.012102407470042</v>
+        <v>-18.0466977830335</v>
       </c>
     </row>
     <row r="84" spans="1:7">
@@ -2312,13 +2312,13 @@
         <v>-10.71072433017574</v>
       </c>
       <c r="E84">
-        <v>-17.49795771523575</v>
+        <v>-35.56799321091589</v>
       </c>
       <c r="F84">
-        <v>0.200165723597562</v>
+        <v>-5.268354701497153</v>
       </c>
       <c r="G84">
-        <v>-5.140084965832014</v>
+        <v>-17.42193843261821</v>
       </c>
     </row>
     <row r="85" spans="1:7">
@@ -2335,13 +2335,13 @@
         <v>-10.55430641151989</v>
       </c>
       <c r="E85">
-        <v>-18.26589633745649</v>
+        <v>-36.65416128707764</v>
       </c>
       <c r="F85">
-        <v>0.4462479995798083</v>
+        <v>-5.543216946154863</v>
       </c>
       <c r="G85">
-        <v>-5.138710133998607</v>
+        <v>-17.02519116836872</v>
       </c>
     </row>
     <row r="86" spans="1:7">
@@ -2358,13 +2358,13 @@
         <v>-10.40172536341779</v>
       </c>
       <c r="E86">
-        <v>-19.60367095795842</v>
+        <v>-36.08328600401169</v>
       </c>
       <c r="F86">
-        <v>0.4667393240228597</v>
+        <v>-5.547771310135455</v>
       </c>
       <c r="G86">
-        <v>-5.057946146534435</v>
+        <v>-17.19332916412857</v>
       </c>
     </row>
     <row r="87" spans="1:7">
@@ -2381,13 +2381,13 @@
         <v>-10.25179410659965</v>
       </c>
       <c r="E87">
-        <v>-20.89864244213985</v>
+        <v>-37.28051943368558</v>
       </c>
       <c r="F87">
-        <v>0.3037547240524457</v>
+        <v>-5.499854397720517</v>
       </c>
       <c r="G87">
-        <v>-5.304900724762923</v>
+        <v>-18.04874854650815</v>
       </c>
     </row>
     <row r="88" spans="1:7">
@@ -2404,13 +2404,13 @@
         <v>-10.10572788696167</v>
       </c>
       <c r="E88">
-        <v>-21.86376440807658</v>
+        <v>-38.39314511923715</v>
       </c>
       <c r="F88">
-        <v>0.2913565491347456</v>
+        <v>-5.447230701722873</v>
       </c>
       <c r="G88">
-        <v>-4.609780499837679</v>
+        <v>-16.84419898714976</v>
       </c>
     </row>
     <row r="89" spans="1:7">
@@ -2427,13 +2427,13 @@
         <v>-9.967189343884147</v>
       </c>
       <c r="E89">
-        <v>-23.16009896293432</v>
+        <v>-39.37553868503913</v>
       </c>
       <c r="F89">
-        <v>0.235986815196821</v>
+        <v>-5.587286920351199</v>
       </c>
       <c r="G89">
-        <v>-4.712253049139137</v>
+        <v>-17.35629923593229</v>
       </c>
     </row>
     <row r="90" spans="1:7">
@@ -2450,13 +2450,13 @@
         <v>-9.833318326421745</v>
       </c>
       <c r="E90">
-        <v>-24.50477950629795</v>
+        <v>-41.1481577578906</v>
       </c>
       <c r="F90">
-        <v>0.09797169384899258</v>
+        <v>-5.871783906270871</v>
       </c>
       <c r="G90">
-        <v>-4.133570252472348</v>
+        <v>-17.29185932572636</v>
       </c>
     </row>
     <row r="91" spans="1:7">
@@ -2473,13 +2473,13 @@
         <v>-9.70684537807448</v>
       </c>
       <c r="E91">
-        <v>-25.48092377796934</v>
+        <v>-41.44933750719274</v>
       </c>
       <c r="F91">
-        <v>0.2239233007098518</v>
+        <v>-5.994175190034497</v>
       </c>
       <c r="G91">
-        <v>-4.332130093920585</v>
+        <v>-17.03104814885234</v>
       </c>
     </row>
     <row r="92" spans="1:7">
@@ -2496,13 +2496,13 @@
         <v>-9.583451227842252</v>
       </c>
       <c r="E92">
-        <v>-27.00211518120395</v>
+        <v>-41.90540918145324</v>
       </c>
       <c r="F92">
-        <v>-0.03837343881479205</v>
+        <v>-5.883684232379488</v>
       </c>
       <c r="G92">
-        <v>-4.529213385667073</v>
+        <v>-16.86846197997107</v>
       </c>
     </row>
     <row r="93" spans="1:7">
@@ -2519,13 +2519,13 @@
         <v>-9.470068725449563</v>
       </c>
       <c r="E93">
-        <v>-29.57484541986366</v>
+        <v>-43.20456723985476</v>
       </c>
       <c r="F93">
-        <v>-0.3524944997933786</v>
+        <v>-5.999763356533783</v>
       </c>
       <c r="G93">
-        <v>-4.056034987022669</v>
+        <v>-16.92610319910584</v>
       </c>
     </row>
     <row r="94" spans="1:7">
@@ -2542,13 +2542,13 @@
         <v>-9.358747035147548</v>
       </c>
       <c r="E94">
-        <v>-32.26857421977131</v>
+        <v>-44.7033426967514</v>
       </c>
       <c r="F94">
-        <v>-0.3266842282569516</v>
+        <v>-6.106653401088822</v>
       </c>
       <c r="G94">
-        <v>-4.471690290508447</v>
+        <v>-17.32841213389857</v>
       </c>
     </row>
     <row r="95" spans="1:7">
@@ -2565,13 +2565,13 @@
         <v>-9.249746786380912</v>
       </c>
       <c r="E95">
-        <v>-33.02256061357442</v>
+        <v>-46.65785698506897</v>
       </c>
       <c r="F95">
-        <v>-0.2680068232796486</v>
+        <v>-6.174167829519191</v>
       </c>
       <c r="G95">
-        <v>-4.34297453117455</v>
+        <v>-17.41111040147204</v>
       </c>
     </row>
     <row r="96" spans="1:7">
@@ -2588,13 +2588,13 @@
         <v>-9.135501454598799</v>
       </c>
       <c r="E96">
-        <v>-35.21898145490773</v>
+        <v>-47.53535750743129</v>
       </c>
       <c r="F96">
-        <v>-0.7497919316870635</v>
+        <v>-6.246587849708937</v>
       </c>
       <c r="G96">
-        <v>-5.176148871991871</v>
+        <v>-17.69384998202783</v>
       </c>
     </row>
     <row r="97" spans="1:7">
@@ -2611,13 +2611,13 @@
         <v>-9.016487769259918</v>
       </c>
       <c r="E97">
-        <v>-37.575966134894</v>
+        <v>-48.62358037867402</v>
       </c>
       <c r="F97">
-        <v>-0.8415750399172487</v>
+        <v>-6.216465097473536</v>
       </c>
       <c r="G97">
-        <v>-5.682785886877933</v>
+        <v>-17.50475974600015</v>
       </c>
     </row>
     <row r="98" spans="1:7">
@@ -2634,13 +2634,13 @@
         <v>-8.885398444121385</v>
       </c>
       <c r="E98">
-        <v>-39.84587958089779</v>
+        <v>-50.10410268896424</v>
       </c>
       <c r="F98">
-        <v>-0.6053321119454549</v>
+        <v>-6.18368080077294</v>
       </c>
       <c r="G98">
-        <v>-5.175351535152926</v>
+        <v>-17.46111129620564</v>
       </c>
     </row>
     <row r="99" spans="1:7">
@@ -2657,13 +2657,13 @@
         <v>-8.739719758995449</v>
       </c>
       <c r="E99">
-        <v>-41.86904100669764</v>
+        <v>-51.23389015888638</v>
       </c>
       <c r="F99">
-        <v>-0.9590532766148717</v>
+        <v>-6.468475998957619</v>
       </c>
       <c r="G99">
-        <v>-5.280137345653793</v>
+        <v>-17.8497769117542</v>
       </c>
     </row>
     <row r="100" spans="1:7">
@@ -2680,13 +2680,13 @@
         <v>-8.569404238579807</v>
       </c>
       <c r="E100">
-        <v>-44.29747594957694</v>
+        <v>-51.86252952427567</v>
       </c>
       <c r="F100">
-        <v>-1.398356391137117</v>
+        <v>-6.641871520446417</v>
       </c>
       <c r="G100">
-        <v>-5.384293161615247</v>
+        <v>-18.7877600316233</v>
       </c>
     </row>
     <row r="101" spans="1:7">
@@ -2703,13 +2703,13 @@
         <v>-8.378941982448566</v>
       </c>
       <c r="E101">
-        <v>-46.09280079110287</v>
+        <v>-52.99949802185548</v>
       </c>
       <c r="F101">
-        <v>-1.325504791530511</v>
+        <v>-6.500728069601916</v>
       </c>
       <c r="G101">
-        <v>-5.489190533649134</v>
+        <v>-18.6353390871332</v>
       </c>
     </row>
     <row r="102" spans="1:7">
@@ -2726,13 +2726,13 @@
         <v>-8.156646545913588</v>
       </c>
       <c r="E102">
-        <v>-48.31923409392202</v>
+        <v>-55.08933669894426</v>
       </c>
       <c r="F102">
-        <v>-1.86536093997638</v>
+        <v>-6.562010690061023</v>
       </c>
       <c r="G102">
-        <v>-5.972455407367272</v>
+        <v>-19.0022780941259</v>
       </c>
     </row>
   </sheetData>
